--- a/labspreadsheet/production/meta/MetaData.xlsx
+++ b/labspreadsheet/production/meta/MetaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laboratoryspreadsheet\labspreadsheet\production\meta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CAA789-6E83-47D9-9FD6-45EA84D945F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F544ED0-AA72-4E5A-A16B-5726A2DDA5E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="789" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-225" windowWidth="38640" windowHeight="21120" tabRatio="789" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="11" r:id="rId1"/>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1418" uniqueCount="304">
   <si>
     <t>TOC</t>
   </si>
@@ -1042,6 +1042,15 @@
   </si>
   <si>
     <t>FX_C4_urinelab</t>
+  </si>
+  <si>
+    <t>Q:\Abteilungsprojekte\eng\EngData\PROJECT_DensifiedActivatedSludge\Project_Werdhölzli\05_RawData</t>
+  </si>
+  <si>
+    <t>ARA_Werdhoelzli</t>
+  </si>
+  <si>
+    <t>AW</t>
   </si>
 </sst>
 </file>
@@ -6520,7 +6529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" style="33" bestFit="1" customWidth="1"/>
@@ -7007,6 +7016,35 @@
         <v>0</v>
       </c>
     </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="D23" s="33">
+        <v>2026</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>291</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="H23" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="33" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="33" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E11" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -7022,9 +7060,10 @@
     <hyperlink ref="E17" r:id="rId11" xr:uid="{C32F76BA-8899-443D-9A90-6C6FEAF6DCA1}"/>
     <hyperlink ref="E21" r:id="rId12" xr:uid="{1B15B64D-3B10-405B-BCA0-7D9F59C8EE48}"/>
     <hyperlink ref="E13" r:id="rId13" xr:uid="{CC17F652-50A5-43EF-9D08-40019F020B54}"/>
+    <hyperlink ref="E23" r:id="rId14" xr:uid="{604EB878-4819-4518-BDC2-F8DA80D4500E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId14"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId15"/>
 </worksheet>
 </file>
 
